--- a/lms_data.xlsx
+++ b/lms_data.xlsx
@@ -9,16 +9,17 @@
   <sheets>
     <sheet name="Users" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Courses" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Enrollments" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Modules" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tasks" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Assignments" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="AssignmentScores" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Exams" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Questions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="ExamResults" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Attendance" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Progress" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Modules" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tasks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Assignments" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AssignmentScores" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Exams" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Questions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ExamResults" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Attendance" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Progress" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Enrollments" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="CourseCompletions" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +459,11 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -488,6 +494,9 @@
       <c r="F2" t="b">
         <v>1</v>
       </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -517,6 +526,9 @@
       </c>
       <c r="F3" t="b">
         <v>1</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -536,50 +548,54 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ExamID</t>
+          <t>AttendanceID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CourseID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>StudentID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Marks</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>TotalMarks</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EXM004</t>
+          <t>ATT001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>CRS001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>USR002</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
@@ -594,13 +610,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>AttendanceID</t>
+          <t>StudentID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -610,24 +626,19 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>StudentID</t>
+          <t>ModuleID</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ATT001</t>
+          <t>USR002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,18 +648,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>USR002</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Present</t>
-        </is>
+          <t>MOD001</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -662,49 +666,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>EnrollmentID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>StudentID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CourseID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ModuleID</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>FinalFee</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ENR001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>USR002</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CRS001</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>89</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10399.2</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CompletionID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>StudentID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>CourseID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CompletedBy</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>CompletedDate</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CertificateID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CERT001</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>USR002</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>CRS001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MOD001</t>
-        </is>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CERT001</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -792,74 +900,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>EnrollmentID</t>
+          <t>ModuleID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>StudentID</t>
+          <t>CourseID</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>CourseID</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Percentage</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Discount</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>FinalFee</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>Link</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ENR001</t>
+          <t>MOD001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>USR002</t>
+          <t>CRS001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CRS001</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>89</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10399.2</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Assigned</t>
+          <t>Python Introduction</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Learning python</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DInMru2Eq6E</t>
         </is>
       </c>
     </row>
@@ -874,20 +968,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>TaskID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>ModuleID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CourseID</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
           <t>Title</t>
@@ -896,38 +990,6 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MOD001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CRS001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Python Introduction</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Learning python</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=DInMru2Eq6E</t>
         </is>
       </c>
     </row>
@@ -942,18 +1004,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TaskID</t>
+          <t>AssignmentID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ModuleID</t>
+          <t>CourseID</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -964,6 +1026,11 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TotalMarks</t>
         </is>
       </c>
     </row>
@@ -978,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -989,22 +1056,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CourseID</t>
+          <t>StudentID</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>TotalMarks</t>
+          <t>Marks</t>
         </is>
       </c>
     </row>
@@ -1019,24 +1076,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>AssignmentID</t>
+          <t>ExamID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>StudentID</t>
+          <t>CourseID</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Marks</t>
-        </is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TotalMarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EXM001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CRS001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EXM002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CRS001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EXM003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CRS001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EXM004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CRS001</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1050,109 +1192,469 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>QuestionID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>ExamID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CourseID</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>TotalMarks</t>
+          <t>OptionA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>OptionB</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>OptionC</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>OptionD</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EXM001</t>
+          <t>QUE001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CRS001</t>
+          <t>EXM004</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>100</v>
+          <t>Which clause sorts results?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SORT BY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ORDER BY</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>GROUP BY</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ARRANGE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EXM002</t>
+          <t>QUE002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CRS001</t>
+          <t>EXM004</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>100</v>
+          <t>Which module is used for regular expressions?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>re</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>regexp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EXM003</t>
+          <t>QUE003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CRS001</t>
+          <t>EXM004</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>python</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
+          <t>Which command adds a record?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CREATE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>UPDATE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>QUE004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>EXM004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CRS001</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
+          <t>What does len() return?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QUE005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EXM004</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>25 x 4?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QUE006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EXM004</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Which collection stores key-value pairs?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Tuple</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dictionary</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QUE007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EXM004</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Which symbol is used for comments?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>/*</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QUE008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EXM004</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ratio 2:3, total 25. First part?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QUE009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EXM004</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Which key uniquely identifies a row?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Foreign Key</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Primary Key</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Unique Key</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Main Key</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QUE010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EXM004</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Which data type is immutable?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dictionary</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tuple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1166,468 +1668,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>QuestionID</t>
+          <t>ExamID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ExamID</t>
+          <t>StudentID</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Marks</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>OptionA</t>
+          <t>TotalMarks</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>OptionB</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>OptionC</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>OptionD</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Answer</t>
+          <t>Date</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUE001</t>
+          <t>EXM004</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EXM004</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Which clause sorts results?</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SORT BY</t>
-        </is>
+          <t>USR002</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ORDER BY</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>GROUP BY</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ARRANGE</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QUE002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>EXM004</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Which module is used for regular expressions?</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>regex</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>re</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>regexp</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>QUE003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>EXM004</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Which command adds a record?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>INSERT</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CREATE</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>UPDATE</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QUE004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>EXM004</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>What does len() return?</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Memory</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QUE005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EXM004</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>25 x 4?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QUE006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>EXM004</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Which collection stores key-value pairs?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Tuple</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Dictionary</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QUE007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>EXM004</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Which symbol is used for comments?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>//</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>/*</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>QUE008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>EXM004</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ratio 2:3, total 25. First part?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>QUE009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>EXM004</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Which key uniquely identifies a row?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Foreign Key</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Primary Key</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Unique Key</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Main Key</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>QUE010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>EXM004</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Which data type is immutable?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Dictionary</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Tuple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
